--- a/outputs/react_configurator_plan.xlsx
+++ b/outputs/react_configurator_plan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" r:id="R5c0670cbdfee48a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кратко" sheetId="2" r:id="Re827be5ea3c04883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" r:id="R5103070da67e4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кратко" sheetId="2" r:id="Re6258013fc31409c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -304,10 +304,12 @@
       <x:c r="E3" t="str">
         <x:v>configurator.html открывается отдельно и готов к монтированию React.</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>Ожидает</x:v>
-      </x:c>
-      <x:c r="G3" t="str"/>
+      <x:c r="F3" s="13" t="str">
+        <x:v>Выполнено</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="str">
+        <x:v>2026-04-24</x:v>
+      </x:c>
       <x:c r="H3" t="str">
         <x:v>0</x:v>
       </x:c>
@@ -861,13 +863,23 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="str">
-        <x:v>Следующий запрос</x:v>
+        <x:v>Выполнено</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>Реализуй часть 1: добавь configurator.html как отдельную страницу для React-конфигуратора.</x:v>
+        <x:v>Часть 1: Страница configurator.html</x:v>
       </x:c>
       <x:c r="C13" t="str"/>
       <x:c r="D13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>Следующий запрос</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Реализуй часть 2: настрой React/Vite только для страницы конфигуратора.</x:v>
+      </x:c>
+      <x:c r="C14" t="str"/>
+      <x:c r="D14" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/react_configurator_plan.xlsx
+++ b/outputs/react_configurator_plan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" r:id="R5103070da67e4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кратко" sheetId="2" r:id="Re6258013fc31409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" r:id="Rf92c12afc27741d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кратко" sheetId="2" r:id="R8848d2d3cbda460b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -330,10 +330,12 @@
       <x:c r="E4" t="str">
         <x:v>React-приложение запускается и рендерит тестовый экран внутри configurator.html.</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
-        <x:v>Ожидает</x:v>
-      </x:c>
-      <x:c r="G4" t="str"/>
+      <x:c r="F4" s="13" t="str">
+        <x:v>Выполнено</x:v>
+      </x:c>
+      <x:c r="G4" s="13" t="str">
+        <x:v>2026-04-24</x:v>
+      </x:c>
       <x:c r="H4" t="str">
         <x:v>1</x:v>
       </x:c>
@@ -873,13 +875,23 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="13" t="str">
-        <x:v>Следующий запрос</x:v>
+        <x:v>Выполнено</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Реализуй часть 2: настрой React/Vite только для страницы конфигуратора.</x:v>
+        <x:v>Часть 2: React/Vite только для конфигуратора</x:v>
       </x:c>
       <x:c r="C14" t="str"/>
       <x:c r="D14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>Следующий запрос</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Реализуй часть 3: свяжи текущий лендинг с configurator.html.</x:v>
+      </x:c>
+      <x:c r="C15" t="str"/>
+      <x:c r="D15" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
